--- a/www/terminologies/CodeSystem-tre-r403-public-activite-smsse-regulee.xlsx
+++ b/www/terminologies/CodeSystem-tre-r403-public-activite-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="391">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-06-29T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>157</t>
+    <t>161</t>
   </si>
   <si>
     <t>Code</t>
@@ -1106,6 +1106,30 @@
   </si>
   <si>
     <t>Personnes sans Domicile</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>Périnatalité</t>
+  </si>
+  <si>
+    <t>842</t>
+  </si>
+  <si>
+    <t>Adultes (sans autre indication)</t>
+  </si>
+  <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>Enfants et adolescents (sans autre indication)</t>
+  </si>
+  <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>Patients de soins sans consentement</t>
   </si>
   <si>
     <t>850</t>
@@ -1624,7 +1648,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3509,7 +3533,7 @@
         <v>380</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>88</v>
+        <v>381</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -3518,12 +3542,60 @@
         <v>74</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D158" s="2"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="D159" s="2"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="D160" s="2"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D161" s="2"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="D162" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/terminologies/CodeSystem-tre-r403-public-activite-smsse-regulee.xlsx
+++ b/www/terminologies/CodeSystem-tre-r403-public-activite-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00.000+00:00</t>
+    <t>2026-02-23T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>161</t>
+    <t>157</t>
   </si>
   <si>
     <t>Code</t>
@@ -1106,30 +1106,6 @@
   </si>
   <si>
     <t>Personnes sans Domicile</t>
-  </si>
-  <si>
-    <t>841</t>
-  </si>
-  <si>
-    <t>Périnatalité</t>
-  </si>
-  <si>
-    <t>842</t>
-  </si>
-  <si>
-    <t>Adultes (sans autre indication)</t>
-  </si>
-  <si>
-    <t>843</t>
-  </si>
-  <si>
-    <t>Enfants et adolescents (sans autre indication)</t>
-  </si>
-  <si>
-    <t>844</t>
-  </si>
-  <si>
-    <t>Patients de soins sans consentement</t>
   </si>
   <si>
     <t>850</t>
@@ -1648,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3533,7 +3509,7 @@
         <v>380</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>381</v>
+        <v>88</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -3542,60 +3518,12 @@
         <v>74</v>
       </c>
       <c r="B158" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="C158" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="D158" s="2"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="D159" s="2"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="D160" s="2"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="D161" s="2"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="D162" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
